--- a/G7_Economic_Data.xlsx
+++ b/G7_Economic_Data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +576,132 @@
         <v>1733.8</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>7412.84</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1490.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>일본</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>62742.57</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.43</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>영국</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10210.31</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2015.35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>캐나다</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>34138.9</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1086.88</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>독일</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>24138.44</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1749.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>프랑스</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>8006.78</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1749.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>이탈리아</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>49264.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1749.6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
